--- a/public/assets/files/Samplemembershipsfile.xlsx
+++ b/public/assets/files/Samplemembershipsfile.xlsx
@@ -1,108 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gulraiz\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D6929F1-C4A2-4609-A834-E2B60A9E7258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C287F894-2E58-4CB0-9DBE-096A6744341D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{930F06E0-8C2B-4FE5-898B-80CDC6C6C97D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Leads" sheetId="1" r:id="rId1"/>
-    <sheet name="Gender" sheetId="2" r:id="rId2"/>
-    <sheet name="City" sheetId="3" r:id="rId3"/>
-    <sheet name="Lead Sopurce" sheetId="4" r:id="rId4"/>
-    <sheet name="Lead Status" sheetId="5" r:id="rId5"/>
-    <sheet name="Treatment" sheetId="6" r:id="rId6"/>
+    <sheet name="Memberships" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="181029"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
-  <si>
-    <t>Gender</t>
-  </si>
-  <si>
-    <t>City</t>
-  </si>
-  <si>
-    <t>Lead Source</t>
-  </si>
-  <si>
-    <t>Lead Status</t>
-  </si>
-  <si>
-    <t>Treatment</t>
-  </si>
-  <si>
-    <t>Patient13</t>
-  </si>
-  <si>
-    <t>Male</t>
-  </si>
-  <si>
-    <t>Lahore</t>
-  </si>
-  <si>
-    <t>Website</t>
-  </si>
-  <si>
-    <t>Open</t>
-  </si>
-  <si>
-    <t>Patient24</t>
-  </si>
-  <si>
-    <t>Female</t>
-  </si>
-  <si>
-    <t>Karachi</t>
-  </si>
-  <si>
-    <t>Islamabad</t>
-  </si>
-  <si>
-    <t>Peshawar</t>
-  </si>
-  <si>
-    <t>Social Media</t>
-  </si>
-  <si>
-    <t>Referral</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Contacted</t>
-  </si>
-  <si>
-    <t>Converted</t>
-  </si>
-  <si>
-    <t>Not Interested</t>
-  </si>
-  <si>
-    <t>Junk</t>
-  </si>
-  <si>
-    <t>Skin Tightening</t>
-  </si>
-  <si>
-    <t>Facial Rejuvenation</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Code</t>
   </si>
@@ -110,14 +33,38 @@
     <t>Membership Type</t>
   </si>
   <si>
-    <t>www</t>
+    <t>Patient2</t>
+  </si>
+  <si>
+    <t>Patient1</t>
+  </si>
+  <si>
+    <t>GOLD</t>
+  </si>
+  <si>
+    <t>SILVER</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -125,21 +72,19 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -151,15 +96,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{A3BAB166-162B-46BB-A00F-AD4078A0747B}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -470,36 +417,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ABE37DB-ED7F-47A7-BC08-3F49B74D1533}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.28515625" customWidth="1"/>
-    <col min="2" max="2" width="22.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.85546875" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -507,172 +455,6 @@
     <hyperlink ref="B2" r:id="rId1" display="Patient@mail.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="B3" r:id="rId2" display="Patient@mail.com" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
-  <pageSetup firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>